--- a/dist/汽车金融合规处罚案例_2026.xlsx
+++ b/dist/汽车金融合规处罚案例_2026.xlsx
@@ -545,7 +545,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>上海金融监管局 · 2026年 · 共 55 条原始记录 · 罚款合计 2,782.73 万元 · 导出时间 2026-06-22 14:22</t>
+          <t>上海金融监管局 · 2026年 · 共 55 条原始记录 · 罚款合计 2,782.73 万元 · 导出时间 2026-06-22 14:30</t>
         </is>
       </c>
     </row>
